--- a/sheets/S08A22P156.xlsx
+++ b/sheets/S08A22P156.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10392" uniqueCount="2657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10384" uniqueCount="2655">
   <si>
     <t>Voter ID</t>
   </si>
@@ -7976,12 +7976,6 @@
   </si>
   <si>
     <t>Ankur Jain</t>
-  </si>
-  <si>
-    <t>Surendra Juneja</t>
-  </si>
-  <si>
-    <t>Nirmal Janeja</t>
   </si>
 </sst>
 </file>
@@ -8362,7 +8356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1299"/>
+  <dimension ref="A1:H1298"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -42120,32 +42114,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1299" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1299" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1299" t="s">
-        <v>2655</v>
-      </c>
-      <c r="C1299" t="s">
-        <v>2656</v>
-      </c>
-      <c r="D1299" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1299" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1299" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1299" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1299" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
